--- a/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="75">
   <si>
     <t>Id</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>#先锋235希望之光</t>
+  </si>
+  <si>
+    <t>#先锋236</t>
   </si>
   <si>
     <t>Center</t>
@@ -1262,7 +1265,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O630"/>
+  <dimension ref="A3:O656"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -11889,7 +11892,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="625" spans="3:7">
+    <row r="625" spans="1:8">
       <c r="C625" s="6">
         <v>23520</v>
       </c>
@@ -11906,7 +11909,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="626" spans="3:7">
+    <row r="626" spans="1:8">
       <c r="C626" s="6">
         <v>23521</v>
       </c>
@@ -11923,7 +11926,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="627" spans="3:7">
+    <row r="627" spans="1:8">
       <c r="C627" s="6">
         <v>23522</v>
       </c>
@@ -11940,7 +11943,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="628" spans="3:7">
+    <row r="628" spans="1:8">
       <c r="C628" s="6">
         <v>23523</v>
       </c>
@@ -11957,7 +11960,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="629" spans="3:7">
+    <row r="629" spans="1:8">
       <c r="C629" s="6">
         <v>23524</v>
       </c>
@@ -11974,7 +11977,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="630" spans="3:7">
+    <row r="630" spans="1:8">
       <c r="C630" s="6">
         <v>23525</v>
       </c>
@@ -11988,6 +11991,448 @@
         <v>42</v>
       </c>
       <c r="G630" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="632" spans="1:8">
+      <c r="A632" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C632" s="6">
+        <v>23601</v>
+      </c>
+      <c r="D632" s="3">
+        <v>236</v>
+      </c>
+      <c r="E632" s="5">
+        <v>1</v>
+      </c>
+      <c r="F632" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G632" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H632" s="3">
+        <v>20375</v>
+      </c>
+    </row>
+    <row r="633" spans="1:8">
+      <c r="A633" s="1"/>
+      <c r="B633" s="1"/>
+      <c r="C633" s="6">
+        <v>23602</v>
+      </c>
+      <c r="D633" s="3">
+        <v>236</v>
+      </c>
+      <c r="E633" s="5">
+        <v>1</v>
+      </c>
+      <c r="F633" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G633" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H633" s="3">
+        <v>20376</v>
+      </c>
+    </row>
+    <row r="634" spans="1:8">
+      <c r="C634" s="6">
+        <v>23603</v>
+      </c>
+      <c r="D634" s="3">
+        <v>236</v>
+      </c>
+      <c r="E634" s="5">
+        <v>1</v>
+      </c>
+      <c r="F634" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G634" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H634" s="3">
+        <v>20377</v>
+      </c>
+    </row>
+    <row r="635" spans="1:8">
+      <c r="C635" s="6">
+        <v>23604</v>
+      </c>
+      <c r="D635" s="3">
+        <v>236</v>
+      </c>
+      <c r="E635" s="3">
+        <v>1</v>
+      </c>
+      <c r="F635" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G635" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H635" s="3">
+        <v>20378</v>
+      </c>
+    </row>
+    <row r="636" spans="1:8">
+      <c r="C636" s="6">
+        <v>23605</v>
+      </c>
+      <c r="D636" s="3">
+        <v>236</v>
+      </c>
+      <c r="E636" s="5">
+        <v>3</v>
+      </c>
+      <c r="F636" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G636" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="637" spans="1:8">
+      <c r="C637" s="6">
+        <v>23606</v>
+      </c>
+      <c r="D637" s="3">
+        <v>236</v>
+      </c>
+      <c r="E637" s="5">
+        <v>10</v>
+      </c>
+      <c r="F637" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G637" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="638" spans="1:8">
+      <c r="C638" s="6">
+        <v>23607</v>
+      </c>
+      <c r="D638" s="3">
+        <v>236</v>
+      </c>
+      <c r="E638" s="5">
+        <v>10</v>
+      </c>
+      <c r="F638" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G638" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="639" spans="1:8">
+      <c r="C639" s="6">
+        <v>23608</v>
+      </c>
+      <c r="D639" s="3">
+        <v>236</v>
+      </c>
+      <c r="E639" s="5">
+        <v>10</v>
+      </c>
+      <c r="F639" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G639" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="640" spans="1:8">
+      <c r="C640" s="6">
+        <v>23609</v>
+      </c>
+      <c r="D640" s="3">
+        <v>236</v>
+      </c>
+      <c r="E640" s="5">
+        <v>10</v>
+      </c>
+      <c r="F640" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G640" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="641" spans="3:7">
+      <c r="C641" s="6">
+        <v>23610</v>
+      </c>
+      <c r="D641" s="3">
+        <v>236</v>
+      </c>
+      <c r="E641" s="5">
+        <v>10</v>
+      </c>
+      <c r="F641" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G641" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="642" spans="3:7">
+      <c r="C642" s="6">
+        <v>23611</v>
+      </c>
+      <c r="D642" s="3">
+        <v>236</v>
+      </c>
+      <c r="E642" s="5">
+        <v>9</v>
+      </c>
+      <c r="F642" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G642" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="643" spans="3:7">
+      <c r="C643" s="6">
+        <v>23612</v>
+      </c>
+      <c r="D643" s="3">
+        <v>236</v>
+      </c>
+      <c r="E643" s="5">
+        <v>10</v>
+      </c>
+      <c r="F643" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G643" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="644" spans="3:7">
+      <c r="C644" s="6">
+        <v>23613</v>
+      </c>
+      <c r="D644" s="3">
+        <v>236</v>
+      </c>
+      <c r="E644" s="5">
+        <v>9</v>
+      </c>
+      <c r="F644" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G644" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="645" spans="3:7">
+      <c r="C645" s="6">
+        <v>23614</v>
+      </c>
+      <c r="D645" s="3">
+        <v>236</v>
+      </c>
+      <c r="E645" s="5">
+        <v>9</v>
+      </c>
+      <c r="F645" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G645" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="646" spans="3:7">
+      <c r="C646" s="6">
+        <v>23615</v>
+      </c>
+      <c r="D646" s="3">
+        <v>236</v>
+      </c>
+      <c r="E646" s="5">
+        <v>9</v>
+      </c>
+      <c r="F646" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G646" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="647" spans="3:7">
+      <c r="C647" s="6">
+        <v>23616</v>
+      </c>
+      <c r="D647" s="3">
+        <v>236</v>
+      </c>
+      <c r="E647" s="5">
+        <v>2</v>
+      </c>
+      <c r="F647" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G647" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="648" spans="3:7">
+      <c r="C648" s="6">
+        <v>23617</v>
+      </c>
+      <c r="D648" s="3">
+        <v>236</v>
+      </c>
+      <c r="E648" s="3">
+        <v>9</v>
+      </c>
+      <c r="F648" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G648" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="649" spans="3:7">
+      <c r="C649" s="6">
+        <v>23618</v>
+      </c>
+      <c r="D649" s="3">
+        <v>236</v>
+      </c>
+      <c r="E649" s="5">
+        <v>9</v>
+      </c>
+      <c r="F649" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G649" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="650" spans="3:7">
+      <c r="C650" s="6">
+        <v>23619</v>
+      </c>
+      <c r="D650" s="3">
+        <v>236</v>
+      </c>
+      <c r="E650" s="5">
+        <v>10</v>
+      </c>
+      <c r="F650" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G650" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="651" spans="3:7">
+      <c r="C651" s="6">
+        <v>23620</v>
+      </c>
+      <c r="D651" s="3">
+        <v>236</v>
+      </c>
+      <c r="E651" s="5">
+        <v>9</v>
+      </c>
+      <c r="F651" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G651" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="652" spans="3:7">
+      <c r="C652" s="6">
+        <v>23621</v>
+      </c>
+      <c r="D652" s="3">
+        <v>236</v>
+      </c>
+      <c r="E652" s="5">
+        <v>5</v>
+      </c>
+      <c r="F652" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G652" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="653" spans="3:7">
+      <c r="C653" s="6">
+        <v>23622</v>
+      </c>
+      <c r="D653" s="3">
+        <v>236</v>
+      </c>
+      <c r="E653" s="5">
+        <v>6</v>
+      </c>
+      <c r="F653" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G653" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="654" spans="3:7">
+      <c r="C654" s="6">
+        <v>23623</v>
+      </c>
+      <c r="D654" s="3">
+        <v>236</v>
+      </c>
+      <c r="E654" s="5">
+        <v>7</v>
+      </c>
+      <c r="F654" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G654" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="655" spans="3:7">
+      <c r="C655" s="6">
+        <v>23624</v>
+      </c>
+      <c r="D655" s="3">
+        <v>236</v>
+      </c>
+      <c r="E655" s="5">
+        <v>8</v>
+      </c>
+      <c r="F655" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G655" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="656" spans="3:7">
+      <c r="C656" s="6">
+        <v>23625</v>
+      </c>
+      <c r="D656" s="3">
+        <v>236</v>
+      </c>
+      <c r="E656" s="5">
+        <v>9</v>
+      </c>
+      <c r="F656" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G656" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12108,10 +12553,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -12126,10 +12571,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -12144,10 +12589,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -12162,10 +12607,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -12182,10 +12627,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -12280,10 +12725,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
@@ -237,7 +237,7 @@
     <t>#先锋235希望之光</t>
   </si>
   <si>
-    <t>#先锋236</t>
+    <t>#先锋236月光神域</t>
   </si>
   <si>
     <t>Center</t>

--- a/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>#先锋236月光神域</t>
+  </si>
+  <si>
+    <t>#先锋237</t>
   </si>
   <si>
     <t>Center</t>
@@ -1265,7 +1268,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O656"/>
+  <dimension ref="A3:O682"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12433,6 +12436,448 @@
         <v>42</v>
       </c>
       <c r="G656" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="658" spans="1:8">
+      <c r="A658" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C658" s="6">
+        <v>23701</v>
+      </c>
+      <c r="D658" s="3">
+        <v>237</v>
+      </c>
+      <c r="E658" s="5">
+        <v>1</v>
+      </c>
+      <c r="F658" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G658" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H658" s="3">
+        <v>20385</v>
+      </c>
+    </row>
+    <row r="659" spans="1:8">
+      <c r="A659" s="1"/>
+      <c r="B659" s="1"/>
+      <c r="C659" s="6">
+        <v>23702</v>
+      </c>
+      <c r="D659" s="3">
+        <v>237</v>
+      </c>
+      <c r="E659" s="5">
+        <v>1</v>
+      </c>
+      <c r="F659" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G659" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H659" s="3">
+        <v>20386</v>
+      </c>
+    </row>
+    <row r="660" spans="1:8">
+      <c r="C660" s="6">
+        <v>23703</v>
+      </c>
+      <c r="D660" s="3">
+        <v>237</v>
+      </c>
+      <c r="E660" s="5">
+        <v>1</v>
+      </c>
+      <c r="F660" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G660" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H660" s="3">
+        <v>20387</v>
+      </c>
+    </row>
+    <row r="661" spans="1:8">
+      <c r="C661" s="6">
+        <v>23704</v>
+      </c>
+      <c r="D661" s="3">
+        <v>237</v>
+      </c>
+      <c r="E661" s="3">
+        <v>1</v>
+      </c>
+      <c r="F661" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G661" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H661" s="3">
+        <v>20388</v>
+      </c>
+    </row>
+    <row r="662" spans="1:8">
+      <c r="C662" s="6">
+        <v>23705</v>
+      </c>
+      <c r="D662" s="3">
+        <v>237</v>
+      </c>
+      <c r="E662" s="5">
+        <v>3</v>
+      </c>
+      <c r="F662" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G662" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="663" spans="1:8">
+      <c r="C663" s="6">
+        <v>23706</v>
+      </c>
+      <c r="D663" s="3">
+        <v>237</v>
+      </c>
+      <c r="E663" s="5">
+        <v>10</v>
+      </c>
+      <c r="F663" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G663" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="664" spans="1:8">
+      <c r="C664" s="6">
+        <v>23707</v>
+      </c>
+      <c r="D664" s="3">
+        <v>237</v>
+      </c>
+      <c r="E664" s="5">
+        <v>10</v>
+      </c>
+      <c r="F664" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G664" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="665" spans="1:8">
+      <c r="C665" s="6">
+        <v>23708</v>
+      </c>
+      <c r="D665" s="3">
+        <v>237</v>
+      </c>
+      <c r="E665" s="5">
+        <v>10</v>
+      </c>
+      <c r="F665" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G665" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="666" spans="1:8">
+      <c r="C666" s="6">
+        <v>23709</v>
+      </c>
+      <c r="D666" s="3">
+        <v>237</v>
+      </c>
+      <c r="E666" s="5">
+        <v>10</v>
+      </c>
+      <c r="F666" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G666" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="667" spans="1:8">
+      <c r="C667" s="6">
+        <v>23710</v>
+      </c>
+      <c r="D667" s="3">
+        <v>237</v>
+      </c>
+      <c r="E667" s="5">
+        <v>10</v>
+      </c>
+      <c r="F667" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G667" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="668" spans="1:8">
+      <c r="C668" s="6">
+        <v>23711</v>
+      </c>
+      <c r="D668" s="3">
+        <v>237</v>
+      </c>
+      <c r="E668" s="5">
+        <v>9</v>
+      </c>
+      <c r="F668" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G668" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="669" spans="1:8">
+      <c r="C669" s="6">
+        <v>23712</v>
+      </c>
+      <c r="D669" s="3">
+        <v>237</v>
+      </c>
+      <c r="E669" s="5">
+        <v>10</v>
+      </c>
+      <c r="F669" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G669" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="670" spans="1:8">
+      <c r="C670" s="6">
+        <v>23713</v>
+      </c>
+      <c r="D670" s="3">
+        <v>237</v>
+      </c>
+      <c r="E670" s="5">
+        <v>9</v>
+      </c>
+      <c r="F670" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G670" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="671" spans="1:8">
+      <c r="C671" s="6">
+        <v>23714</v>
+      </c>
+      <c r="D671" s="3">
+        <v>237</v>
+      </c>
+      <c r="E671" s="5">
+        <v>9</v>
+      </c>
+      <c r="F671" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G671" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="672" spans="1:8">
+      <c r="C672" s="6">
+        <v>23715</v>
+      </c>
+      <c r="D672" s="3">
+        <v>237</v>
+      </c>
+      <c r="E672" s="5">
+        <v>9</v>
+      </c>
+      <c r="F672" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G672" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="673" spans="3:7">
+      <c r="C673" s="6">
+        <v>23716</v>
+      </c>
+      <c r="D673" s="3">
+        <v>237</v>
+      </c>
+      <c r="E673" s="5">
+        <v>2</v>
+      </c>
+      <c r="F673" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G673" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="674" spans="3:7">
+      <c r="C674" s="6">
+        <v>23717</v>
+      </c>
+      <c r="D674" s="3">
+        <v>237</v>
+      </c>
+      <c r="E674" s="3">
+        <v>9</v>
+      </c>
+      <c r="F674" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G674" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="675" spans="3:7">
+      <c r="C675" s="6">
+        <v>23718</v>
+      </c>
+      <c r="D675" s="3">
+        <v>237</v>
+      </c>
+      <c r="E675" s="5">
+        <v>9</v>
+      </c>
+      <c r="F675" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G675" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="676" spans="3:7">
+      <c r="C676" s="6">
+        <v>23719</v>
+      </c>
+      <c r="D676" s="3">
+        <v>237</v>
+      </c>
+      <c r="E676" s="5">
+        <v>10</v>
+      </c>
+      <c r="F676" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G676" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="677" spans="3:7">
+      <c r="C677" s="6">
+        <v>23720</v>
+      </c>
+      <c r="D677" s="3">
+        <v>237</v>
+      </c>
+      <c r="E677" s="5">
+        <v>9</v>
+      </c>
+      <c r="F677" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G677" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="678" spans="3:7">
+      <c r="C678" s="6">
+        <v>23721</v>
+      </c>
+      <c r="D678" s="3">
+        <v>237</v>
+      </c>
+      <c r="E678" s="5">
+        <v>5</v>
+      </c>
+      <c r="F678" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G678" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="679" spans="3:7">
+      <c r="C679" s="6">
+        <v>23722</v>
+      </c>
+      <c r="D679" s="3">
+        <v>237</v>
+      </c>
+      <c r="E679" s="5">
+        <v>6</v>
+      </c>
+      <c r="F679" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G679" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="680" spans="3:7">
+      <c r="C680" s="6">
+        <v>23723</v>
+      </c>
+      <c r="D680" s="3">
+        <v>237</v>
+      </c>
+      <c r="E680" s="5">
+        <v>7</v>
+      </c>
+      <c r="F680" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G680" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="681" spans="3:7">
+      <c r="C681" s="6">
+        <v>23724</v>
+      </c>
+      <c r="D681" s="3">
+        <v>237</v>
+      </c>
+      <c r="E681" s="5">
+        <v>8</v>
+      </c>
+      <c r="F681" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G681" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="682" spans="3:7">
+      <c r="C682" s="6">
+        <v>23725</v>
+      </c>
+      <c r="D682" s="3">
+        <v>237</v>
+      </c>
+      <c r="E682" s="5">
+        <v>9</v>
+      </c>
+      <c r="F682" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G682" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12553,10 +12998,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -12571,10 +13016,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -12589,10 +13034,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -12607,10 +13052,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -12627,10 +13072,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -12725,10 +13170,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11775"/>
+    <workbookView windowWidth="26745" windowHeight="12345"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -240,7 +240,7 @@
     <t>#先锋236月光神域</t>
   </si>
   <si>
-    <t>#先锋237</t>
+    <t>#先锋237霜火之巅</t>
   </si>
   <si>
     <t>Center</t>

--- a/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="26745" windowHeight="12345"/>
+    <workbookView windowWidth="27945" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="77">
   <si>
     <t>Id</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>#先锋237霜火之巅</t>
+  </si>
+  <si>
+    <t>#先锋238盛世华章</t>
   </si>
   <si>
     <t>Center</t>
@@ -1268,7 +1271,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O682"/>
+  <dimension ref="A3:O708"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12711,7 +12714,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="673" spans="3:7">
+    <row r="673" spans="1:8">
       <c r="C673" s="6">
         <v>23716</v>
       </c>
@@ -12728,7 +12731,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="674" spans="3:7">
+    <row r="674" spans="1:8">
       <c r="C674" s="6">
         <v>23717</v>
       </c>
@@ -12745,7 +12748,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="675" spans="3:7">
+    <row r="675" spans="1:8">
       <c r="C675" s="6">
         <v>23718</v>
       </c>
@@ -12762,7 +12765,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="676" spans="3:7">
+    <row r="676" spans="1:8">
       <c r="C676" s="6">
         <v>23719</v>
       </c>
@@ -12779,7 +12782,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="677" spans="3:7">
+    <row r="677" spans="1:8">
       <c r="C677" s="6">
         <v>23720</v>
       </c>
@@ -12796,7 +12799,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="678" spans="3:7">
+    <row r="678" spans="1:8">
       <c r="C678" s="6">
         <v>23721</v>
       </c>
@@ -12813,7 +12816,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="679" spans="3:7">
+    <row r="679" spans="1:8">
       <c r="C679" s="6">
         <v>23722</v>
       </c>
@@ -12830,7 +12833,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="680" spans="3:7">
+    <row r="680" spans="1:8">
       <c r="C680" s="6">
         <v>23723</v>
       </c>
@@ -12847,7 +12850,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="681" spans="3:7">
+    <row r="681" spans="1:8">
       <c r="C681" s="6">
         <v>23724</v>
       </c>
@@ -12864,7 +12867,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="682" spans="3:7">
+    <row r="682" spans="1:8">
       <c r="C682" s="6">
         <v>23725</v>
       </c>
@@ -12878,6 +12881,448 @@
         <v>42</v>
       </c>
       <c r="G682" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8">
+      <c r="A684" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C684" s="6">
+        <v>23801</v>
+      </c>
+      <c r="D684" s="3">
+        <v>238</v>
+      </c>
+      <c r="E684" s="5">
+        <v>1</v>
+      </c>
+      <c r="F684" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G684" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H684" s="3">
+        <v>20415</v>
+      </c>
+    </row>
+    <row r="685" spans="1:8">
+      <c r="A685" s="1"/>
+      <c r="B685" s="1"/>
+      <c r="C685" s="6">
+        <v>23802</v>
+      </c>
+      <c r="D685" s="3">
+        <v>238</v>
+      </c>
+      <c r="E685" s="5">
+        <v>1</v>
+      </c>
+      <c r="F685" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G685" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H685" s="3">
+        <v>20416</v>
+      </c>
+    </row>
+    <row r="686" spans="1:8">
+      <c r="C686" s="6">
+        <v>23803</v>
+      </c>
+      <c r="D686" s="3">
+        <v>238</v>
+      </c>
+      <c r="E686" s="5">
+        <v>1</v>
+      </c>
+      <c r="F686" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G686" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H686" s="3">
+        <v>20417</v>
+      </c>
+    </row>
+    <row r="687" spans="1:8">
+      <c r="C687" s="6">
+        <v>23804</v>
+      </c>
+      <c r="D687" s="3">
+        <v>238</v>
+      </c>
+      <c r="E687" s="3">
+        <v>1</v>
+      </c>
+      <c r="F687" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G687" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H687" s="3">
+        <v>20418</v>
+      </c>
+    </row>
+    <row r="688" spans="1:8">
+      <c r="C688" s="6">
+        <v>23805</v>
+      </c>
+      <c r="D688" s="3">
+        <v>238</v>
+      </c>
+      <c r="E688" s="5">
+        <v>3</v>
+      </c>
+      <c r="F688" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G688" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="689" spans="3:7">
+      <c r="C689" s="6">
+        <v>23806</v>
+      </c>
+      <c r="D689" s="3">
+        <v>238</v>
+      </c>
+      <c r="E689" s="5">
+        <v>10</v>
+      </c>
+      <c r="F689" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G689" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="690" spans="3:7">
+      <c r="C690" s="6">
+        <v>23807</v>
+      </c>
+      <c r="D690" s="3">
+        <v>238</v>
+      </c>
+      <c r="E690" s="5">
+        <v>10</v>
+      </c>
+      <c r="F690" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G690" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="691" spans="3:7">
+      <c r="C691" s="6">
+        <v>23808</v>
+      </c>
+      <c r="D691" s="3">
+        <v>238</v>
+      </c>
+      <c r="E691" s="5">
+        <v>10</v>
+      </c>
+      <c r="F691" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G691" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="692" spans="3:7">
+      <c r="C692" s="6">
+        <v>23809</v>
+      </c>
+      <c r="D692" s="3">
+        <v>238</v>
+      </c>
+      <c r="E692" s="5">
+        <v>10</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G692" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="693" spans="3:7">
+      <c r="C693" s="6">
+        <v>23810</v>
+      </c>
+      <c r="D693" s="3">
+        <v>238</v>
+      </c>
+      <c r="E693" s="5">
+        <v>10</v>
+      </c>
+      <c r="F693" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G693" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="694" spans="3:7">
+      <c r="C694" s="6">
+        <v>23811</v>
+      </c>
+      <c r="D694" s="3">
+        <v>238</v>
+      </c>
+      <c r="E694" s="5">
+        <v>9</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G694" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="695" spans="3:7">
+      <c r="C695" s="6">
+        <v>23812</v>
+      </c>
+      <c r="D695" s="3">
+        <v>238</v>
+      </c>
+      <c r="E695" s="5">
+        <v>10</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G695" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="696" spans="3:7">
+      <c r="C696" s="6">
+        <v>23813</v>
+      </c>
+      <c r="D696" s="3">
+        <v>238</v>
+      </c>
+      <c r="E696" s="5">
+        <v>9</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G696" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="697" spans="3:7">
+      <c r="C697" s="6">
+        <v>23814</v>
+      </c>
+      <c r="D697" s="3">
+        <v>238</v>
+      </c>
+      <c r="E697" s="5">
+        <v>9</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G697" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="698" spans="3:7">
+      <c r="C698" s="6">
+        <v>23815</v>
+      </c>
+      <c r="D698" s="3">
+        <v>238</v>
+      </c>
+      <c r="E698" s="5">
+        <v>9</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G698" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="699" spans="3:7">
+      <c r="C699" s="6">
+        <v>23816</v>
+      </c>
+      <c r="D699" s="3">
+        <v>238</v>
+      </c>
+      <c r="E699" s="5">
+        <v>2</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G699" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="700" spans="3:7">
+      <c r="C700" s="6">
+        <v>23817</v>
+      </c>
+      <c r="D700" s="3">
+        <v>238</v>
+      </c>
+      <c r="E700" s="3">
+        <v>9</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G700" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="701" spans="3:7">
+      <c r="C701" s="6">
+        <v>23818</v>
+      </c>
+      <c r="D701" s="3">
+        <v>238</v>
+      </c>
+      <c r="E701" s="5">
+        <v>9</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G701" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="702" spans="3:7">
+      <c r="C702" s="6">
+        <v>23819</v>
+      </c>
+      <c r="D702" s="3">
+        <v>238</v>
+      </c>
+      <c r="E702" s="5">
+        <v>10</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G702" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="703" spans="3:7">
+      <c r="C703" s="6">
+        <v>23820</v>
+      </c>
+      <c r="D703" s="3">
+        <v>238</v>
+      </c>
+      <c r="E703" s="5">
+        <v>9</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G703" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="704" spans="3:7">
+      <c r="C704" s="6">
+        <v>23821</v>
+      </c>
+      <c r="D704" s="3">
+        <v>238</v>
+      </c>
+      <c r="E704" s="5">
+        <v>5</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G704" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="705" spans="3:7">
+      <c r="C705" s="6">
+        <v>23822</v>
+      </c>
+      <c r="D705" s="3">
+        <v>238</v>
+      </c>
+      <c r="E705" s="5">
+        <v>6</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G705" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="706" spans="3:7">
+      <c r="C706" s="6">
+        <v>23823</v>
+      </c>
+      <c r="D706" s="3">
+        <v>238</v>
+      </c>
+      <c r="E706" s="5">
+        <v>7</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G706" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="707" spans="3:7">
+      <c r="C707" s="6">
+        <v>23824</v>
+      </c>
+      <c r="D707" s="3">
+        <v>238</v>
+      </c>
+      <c r="E707" s="5">
+        <v>8</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G707" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="708" spans="3:7">
+      <c r="C708" s="6">
+        <v>23825</v>
+      </c>
+      <c r="D708" s="3">
+        <v>238</v>
+      </c>
+      <c r="E708" s="5">
+        <v>9</v>
+      </c>
+      <c r="F708" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G708" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12998,10 +13443,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13016,10 +13461,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13034,10 +13479,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13052,10 +13497,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13072,10 +13517,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -13170,10 +13615,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="78">
   <si>
     <t>Id</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>#先锋238盛世华章</t>
+  </si>
+  <si>
+    <t>#先锋239翡翠之地</t>
   </si>
   <si>
     <t>Center</t>
@@ -1271,7 +1274,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O708"/>
+  <dimension ref="A3:O734"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13258,7 +13261,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="705" spans="3:7">
+    <row r="705" spans="1:8">
       <c r="C705" s="6">
         <v>23822</v>
       </c>
@@ -13275,7 +13278,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="706" spans="3:7">
+    <row r="706" spans="1:8">
       <c r="C706" s="6">
         <v>23823</v>
       </c>
@@ -13292,7 +13295,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="707" spans="3:7">
+    <row r="707" spans="1:8">
       <c r="C707" s="6">
         <v>23824</v>
       </c>
@@ -13309,7 +13312,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="708" spans="3:7">
+    <row r="708" spans="1:8">
       <c r="C708" s="6">
         <v>23825</v>
       </c>
@@ -13323,6 +13326,448 @@
         <v>42</v>
       </c>
       <c r="G708" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="710" spans="1:8">
+      <c r="A710" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C710" s="6">
+        <v>23901</v>
+      </c>
+      <c r="D710" s="3">
+        <v>239</v>
+      </c>
+      <c r="E710" s="5">
+        <v>1</v>
+      </c>
+      <c r="F710" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G710" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H710" s="3">
+        <v>20435</v>
+      </c>
+    </row>
+    <row r="711" spans="1:8">
+      <c r="A711" s="1"/>
+      <c r="B711" s="1"/>
+      <c r="C711" s="6">
+        <v>23902</v>
+      </c>
+      <c r="D711" s="3">
+        <v>239</v>
+      </c>
+      <c r="E711" s="5">
+        <v>1</v>
+      </c>
+      <c r="F711" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G711" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H711" s="3">
+        <v>20436</v>
+      </c>
+    </row>
+    <row r="712" spans="1:8">
+      <c r="C712" s="6">
+        <v>23903</v>
+      </c>
+      <c r="D712" s="3">
+        <v>239</v>
+      </c>
+      <c r="E712" s="5">
+        <v>1</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G712" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H712" s="3">
+        <v>20437</v>
+      </c>
+    </row>
+    <row r="713" spans="1:8">
+      <c r="C713" s="6">
+        <v>23904</v>
+      </c>
+      <c r="D713" s="3">
+        <v>239</v>
+      </c>
+      <c r="E713" s="3">
+        <v>1</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G713" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H713" s="3">
+        <v>20438</v>
+      </c>
+    </row>
+    <row r="714" spans="1:8">
+      <c r="C714" s="6">
+        <v>23905</v>
+      </c>
+      <c r="D714" s="3">
+        <v>239</v>
+      </c>
+      <c r="E714" s="5">
+        <v>3</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G714" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="715" spans="1:8">
+      <c r="C715" s="6">
+        <v>23906</v>
+      </c>
+      <c r="D715" s="3">
+        <v>239</v>
+      </c>
+      <c r="E715" s="5">
+        <v>10</v>
+      </c>
+      <c r="F715" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G715" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="716" spans="1:8">
+      <c r="C716" s="6">
+        <v>23907</v>
+      </c>
+      <c r="D716" s="3">
+        <v>239</v>
+      </c>
+      <c r="E716" s="5">
+        <v>10</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G716" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="717" spans="1:8">
+      <c r="C717" s="6">
+        <v>23908</v>
+      </c>
+      <c r="D717" s="3">
+        <v>239</v>
+      </c>
+      <c r="E717" s="5">
+        <v>10</v>
+      </c>
+      <c r="F717" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G717" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="718" spans="1:8">
+      <c r="C718" s="6">
+        <v>23909</v>
+      </c>
+      <c r="D718" s="3">
+        <v>239</v>
+      </c>
+      <c r="E718" s="5">
+        <v>10</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G718" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="719" spans="1:8">
+      <c r="C719" s="6">
+        <v>23910</v>
+      </c>
+      <c r="D719" s="3">
+        <v>239</v>
+      </c>
+      <c r="E719" s="5">
+        <v>10</v>
+      </c>
+      <c r="F719" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G719" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="720" spans="1:8">
+      <c r="C720" s="6">
+        <v>23911</v>
+      </c>
+      <c r="D720" s="3">
+        <v>239</v>
+      </c>
+      <c r="E720" s="5">
+        <v>9</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G720" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="721" spans="3:7">
+      <c r="C721" s="6">
+        <v>23912</v>
+      </c>
+      <c r="D721" s="3">
+        <v>239</v>
+      </c>
+      <c r="E721" s="5">
+        <v>10</v>
+      </c>
+      <c r="F721" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G721" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="722" spans="3:7">
+      <c r="C722" s="6">
+        <v>23913</v>
+      </c>
+      <c r="D722" s="3">
+        <v>239</v>
+      </c>
+      <c r="E722" s="5">
+        <v>9</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G722" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="723" spans="3:7">
+      <c r="C723" s="6">
+        <v>23914</v>
+      </c>
+      <c r="D723" s="3">
+        <v>239</v>
+      </c>
+      <c r="E723" s="5">
+        <v>9</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G723" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="724" spans="3:7">
+      <c r="C724" s="6">
+        <v>23915</v>
+      </c>
+      <c r="D724" s="3">
+        <v>239</v>
+      </c>
+      <c r="E724" s="5">
+        <v>9</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G724" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="725" spans="3:7">
+      <c r="C725" s="6">
+        <v>23916</v>
+      </c>
+      <c r="D725" s="3">
+        <v>239</v>
+      </c>
+      <c r="E725" s="5">
+        <v>2</v>
+      </c>
+      <c r="F725" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G725" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="726" spans="3:7">
+      <c r="C726" s="6">
+        <v>23917</v>
+      </c>
+      <c r="D726" s="3">
+        <v>239</v>
+      </c>
+      <c r="E726" s="3">
+        <v>9</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G726" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="727" spans="3:7">
+      <c r="C727" s="6">
+        <v>23918</v>
+      </c>
+      <c r="D727" s="3">
+        <v>239</v>
+      </c>
+      <c r="E727" s="5">
+        <v>9</v>
+      </c>
+      <c r="F727" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G727" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="728" spans="3:7">
+      <c r="C728" s="6">
+        <v>23919</v>
+      </c>
+      <c r="D728" s="3">
+        <v>239</v>
+      </c>
+      <c r="E728" s="5">
+        <v>10</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G728" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="729" spans="3:7">
+      <c r="C729" s="6">
+        <v>23920</v>
+      </c>
+      <c r="D729" s="3">
+        <v>239</v>
+      </c>
+      <c r="E729" s="5">
+        <v>9</v>
+      </c>
+      <c r="F729" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G729" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="730" spans="3:7">
+      <c r="C730" s="6">
+        <v>23921</v>
+      </c>
+      <c r="D730" s="3">
+        <v>239</v>
+      </c>
+      <c r="E730" s="5">
+        <v>5</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G730" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="731" spans="3:7">
+      <c r="C731" s="6">
+        <v>23922</v>
+      </c>
+      <c r="D731" s="3">
+        <v>239</v>
+      </c>
+      <c r="E731" s="5">
+        <v>6</v>
+      </c>
+      <c r="F731" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G731" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="732" spans="3:7">
+      <c r="C732" s="6">
+        <v>23923</v>
+      </c>
+      <c r="D732" s="3">
+        <v>239</v>
+      </c>
+      <c r="E732" s="5">
+        <v>7</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G732" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="733" spans="3:7">
+      <c r="C733" s="6">
+        <v>23924</v>
+      </c>
+      <c r="D733" s="3">
+        <v>239</v>
+      </c>
+      <c r="E733" s="5">
+        <v>8</v>
+      </c>
+      <c r="F733" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G733" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="734" spans="3:7">
+      <c r="C734" s="6">
+        <v>23925</v>
+      </c>
+      <c r="D734" s="3">
+        <v>239</v>
+      </c>
+      <c r="E734" s="5">
+        <v>9</v>
+      </c>
+      <c r="F734" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G734" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13443,10 +13888,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13461,10 +13906,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13479,10 +13924,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13497,10 +13942,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13517,10 +13962,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -13615,10 +14060,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing20220362\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="79">
   <si>
     <t>Id</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>#先锋239翡翠之地</t>
+  </si>
+  <si>
+    <t>#先锋240</t>
   </si>
   <si>
     <t>Center</t>
@@ -1274,7 +1277,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O734"/>
+  <dimension ref="A3:O760"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13533,7 +13536,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="721" spans="3:7">
+    <row r="721" spans="1:8">
       <c r="C721" s="6">
         <v>23912</v>
       </c>
@@ -13550,7 +13553,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="722" spans="3:7">
+    <row r="722" spans="1:8">
       <c r="C722" s="6">
         <v>23913</v>
       </c>
@@ -13567,7 +13570,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="723" spans="3:7">
+    <row r="723" spans="1:8">
       <c r="C723" s="6">
         <v>23914</v>
       </c>
@@ -13584,7 +13587,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="724" spans="3:7">
+    <row r="724" spans="1:8">
       <c r="C724" s="6">
         <v>23915</v>
       </c>
@@ -13601,7 +13604,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="725" spans="3:7">
+    <row r="725" spans="1:8">
       <c r="C725" s="6">
         <v>23916</v>
       </c>
@@ -13618,7 +13621,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="726" spans="3:7">
+    <row r="726" spans="1:8">
       <c r="C726" s="6">
         <v>23917</v>
       </c>
@@ -13635,7 +13638,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="727" spans="3:7">
+    <row r="727" spans="1:8">
       <c r="C727" s="6">
         <v>23918</v>
       </c>
@@ -13652,7 +13655,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="728" spans="3:7">
+    <row r="728" spans="1:8">
       <c r="C728" s="6">
         <v>23919</v>
       </c>
@@ -13669,7 +13672,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="729" spans="3:7">
+    <row r="729" spans="1:8">
       <c r="C729" s="6">
         <v>23920</v>
       </c>
@@ -13686,7 +13689,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="730" spans="3:7">
+    <row r="730" spans="1:8">
       <c r="C730" s="6">
         <v>23921</v>
       </c>
@@ -13703,7 +13706,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="731" spans="3:7">
+    <row r="731" spans="1:8">
       <c r="C731" s="6">
         <v>23922</v>
       </c>
@@ -13720,7 +13723,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="732" spans="3:7">
+    <row r="732" spans="1:8">
       <c r="C732" s="6">
         <v>23923</v>
       </c>
@@ -13737,7 +13740,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="733" spans="3:7">
+    <row r="733" spans="1:8">
       <c r="C733" s="6">
         <v>23924</v>
       </c>
@@ -13754,7 +13757,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="734" spans="3:7">
+    <row r="734" spans="1:8">
       <c r="C734" s="6">
         <v>23925</v>
       </c>
@@ -13768,6 +13771,448 @@
         <v>42</v>
       </c>
       <c r="G734" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="736" spans="1:8">
+      <c r="A736" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C736" s="6">
+        <v>24001</v>
+      </c>
+      <c r="D736" s="3">
+        <v>240</v>
+      </c>
+      <c r="E736" s="5">
+        <v>1</v>
+      </c>
+      <c r="F736" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G736" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H736" s="3">
+        <v>20455</v>
+      </c>
+    </row>
+    <row r="737" spans="1:8">
+      <c r="A737" s="1"/>
+      <c r="B737" s="1"/>
+      <c r="C737" s="6">
+        <v>24002</v>
+      </c>
+      <c r="D737" s="3">
+        <v>240</v>
+      </c>
+      <c r="E737" s="5">
+        <v>1</v>
+      </c>
+      <c r="F737" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G737" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H737" s="3">
+        <v>20456</v>
+      </c>
+    </row>
+    <row r="738" spans="1:8">
+      <c r="C738" s="6">
+        <v>24003</v>
+      </c>
+      <c r="D738" s="3">
+        <v>240</v>
+      </c>
+      <c r="E738" s="5">
+        <v>1</v>
+      </c>
+      <c r="F738" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G738" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H738" s="3">
+        <v>20457</v>
+      </c>
+    </row>
+    <row r="739" spans="1:8">
+      <c r="C739" s="6">
+        <v>24004</v>
+      </c>
+      <c r="D739" s="3">
+        <v>240</v>
+      </c>
+      <c r="E739" s="3">
+        <v>1</v>
+      </c>
+      <c r="F739" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G739" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H739" s="3">
+        <v>20458</v>
+      </c>
+    </row>
+    <row r="740" spans="1:8">
+      <c r="C740" s="6">
+        <v>24005</v>
+      </c>
+      <c r="D740" s="3">
+        <v>240</v>
+      </c>
+      <c r="E740" s="5">
+        <v>3</v>
+      </c>
+      <c r="F740" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G740" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="741" spans="1:8">
+      <c r="C741" s="6">
+        <v>24006</v>
+      </c>
+      <c r="D741" s="3">
+        <v>240</v>
+      </c>
+      <c r="E741" s="5">
+        <v>10</v>
+      </c>
+      <c r="F741" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G741" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="742" spans="1:8">
+      <c r="C742" s="6">
+        <v>24007</v>
+      </c>
+      <c r="D742" s="3">
+        <v>240</v>
+      </c>
+      <c r="E742" s="5">
+        <v>10</v>
+      </c>
+      <c r="F742" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G742" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="743" spans="1:8">
+      <c r="C743" s="6">
+        <v>24008</v>
+      </c>
+      <c r="D743" s="3">
+        <v>240</v>
+      </c>
+      <c r="E743" s="5">
+        <v>10</v>
+      </c>
+      <c r="F743" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G743" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="744" spans="1:8">
+      <c r="C744" s="6">
+        <v>24009</v>
+      </c>
+      <c r="D744" s="3">
+        <v>240</v>
+      </c>
+      <c r="E744" s="5">
+        <v>10</v>
+      </c>
+      <c r="F744" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G744" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="745" spans="1:8">
+      <c r="C745" s="6">
+        <v>24010</v>
+      </c>
+      <c r="D745" s="3">
+        <v>240</v>
+      </c>
+      <c r="E745" s="5">
+        <v>10</v>
+      </c>
+      <c r="F745" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G745" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="746" spans="1:8">
+      <c r="C746" s="6">
+        <v>24011</v>
+      </c>
+      <c r="D746" s="3">
+        <v>240</v>
+      </c>
+      <c r="E746" s="5">
+        <v>9</v>
+      </c>
+      <c r="F746" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G746" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="747" spans="1:8">
+      <c r="C747" s="6">
+        <v>24012</v>
+      </c>
+      <c r="D747" s="3">
+        <v>240</v>
+      </c>
+      <c r="E747" s="5">
+        <v>10</v>
+      </c>
+      <c r="F747" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G747" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="748" spans="1:8">
+      <c r="C748" s="6">
+        <v>24013</v>
+      </c>
+      <c r="D748" s="3">
+        <v>240</v>
+      </c>
+      <c r="E748" s="5">
+        <v>9</v>
+      </c>
+      <c r="F748" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G748" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="749" spans="1:8">
+      <c r="C749" s="6">
+        <v>24014</v>
+      </c>
+      <c r="D749" s="3">
+        <v>240</v>
+      </c>
+      <c r="E749" s="5">
+        <v>9</v>
+      </c>
+      <c r="F749" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G749" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="750" spans="1:8">
+      <c r="C750" s="6">
+        <v>24015</v>
+      </c>
+      <c r="D750" s="3">
+        <v>240</v>
+      </c>
+      <c r="E750" s="5">
+        <v>9</v>
+      </c>
+      <c r="F750" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G750" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="751" spans="1:8">
+      <c r="C751" s="6">
+        <v>24016</v>
+      </c>
+      <c r="D751" s="3">
+        <v>240</v>
+      </c>
+      <c r="E751" s="5">
+        <v>2</v>
+      </c>
+      <c r="F751" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G751" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="752" spans="1:8">
+      <c r="C752" s="6">
+        <v>24017</v>
+      </c>
+      <c r="D752" s="3">
+        <v>240</v>
+      </c>
+      <c r="E752" s="3">
+        <v>9</v>
+      </c>
+      <c r="F752" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G752" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="753" spans="3:7">
+      <c r="C753" s="6">
+        <v>24018</v>
+      </c>
+      <c r="D753" s="3">
+        <v>240</v>
+      </c>
+      <c r="E753" s="5">
+        <v>9</v>
+      </c>
+      <c r="F753" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G753" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="754" spans="3:7">
+      <c r="C754" s="6">
+        <v>24019</v>
+      </c>
+      <c r="D754" s="3">
+        <v>240</v>
+      </c>
+      <c r="E754" s="5">
+        <v>10</v>
+      </c>
+      <c r="F754" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G754" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="755" spans="3:7">
+      <c r="C755" s="6">
+        <v>24020</v>
+      </c>
+      <c r="D755" s="3">
+        <v>240</v>
+      </c>
+      <c r="E755" s="5">
+        <v>9</v>
+      </c>
+      <c r="F755" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G755" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="756" spans="3:7">
+      <c r="C756" s="6">
+        <v>24021</v>
+      </c>
+      <c r="D756" s="3">
+        <v>240</v>
+      </c>
+      <c r="E756" s="5">
+        <v>5</v>
+      </c>
+      <c r="F756" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G756" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="757" spans="3:7">
+      <c r="C757" s="6">
+        <v>24022</v>
+      </c>
+      <c r="D757" s="3">
+        <v>240</v>
+      </c>
+      <c r="E757" s="5">
+        <v>6</v>
+      </c>
+      <c r="F757" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G757" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="758" spans="3:7">
+      <c r="C758" s="6">
+        <v>24023</v>
+      </c>
+      <c r="D758" s="3">
+        <v>240</v>
+      </c>
+      <c r="E758" s="5">
+        <v>7</v>
+      </c>
+      <c r="F758" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G758" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="759" spans="3:7">
+      <c r="C759" s="6">
+        <v>24024</v>
+      </c>
+      <c r="D759" s="3">
+        <v>240</v>
+      </c>
+      <c r="E759" s="5">
+        <v>8</v>
+      </c>
+      <c r="F759" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G759" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="760" spans="3:7">
+      <c r="C760" s="6">
+        <v>24025</v>
+      </c>
+      <c r="D760" s="3">
+        <v>240</v>
+      </c>
+      <c r="E760" s="5">
+        <v>9</v>
+      </c>
+      <c r="F760" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G760" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13888,10 +14333,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13906,10 +14351,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13924,10 +14369,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13942,10 +14387,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13962,10 +14407,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -14060,10 +14505,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing20220362\Excel\StartConfig\LocalhostOld\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -249,7 +249,7 @@
     <t>#先锋239翡翠之地</t>
   </si>
   <si>
-    <t>#先锋240</t>
+    <t>#先锋240青野拾光</t>
   </si>
   <si>
     <t>Center</t>

--- a/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="80">
   <si>
     <t>Id</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>#先锋240青野拾光</t>
+  </si>
+  <si>
+    <t>#先锋241</t>
   </si>
   <si>
     <t>Center</t>
@@ -1277,7 +1280,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O760"/>
+  <dimension ref="A3:O786"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -14080,7 +14083,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="753" spans="3:7">
+    <row r="753" spans="1:8">
       <c r="C753" s="6">
         <v>24018</v>
       </c>
@@ -14097,7 +14100,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="754" spans="3:7">
+    <row r="754" spans="1:8">
       <c r="C754" s="6">
         <v>24019</v>
       </c>
@@ -14114,7 +14117,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="755" spans="3:7">
+    <row r="755" spans="1:8">
       <c r="C755" s="6">
         <v>24020</v>
       </c>
@@ -14131,7 +14134,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="756" spans="3:7">
+    <row r="756" spans="1:8">
       <c r="C756" s="6">
         <v>24021</v>
       </c>
@@ -14148,7 +14151,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="757" spans="3:7">
+    <row r="757" spans="1:8">
       <c r="C757" s="6">
         <v>24022</v>
       </c>
@@ -14165,7 +14168,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="758" spans="3:7">
+    <row r="758" spans="1:8">
       <c r="C758" s="6">
         <v>24023</v>
       </c>
@@ -14182,7 +14185,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="759" spans="3:7">
+    <row r="759" spans="1:8">
       <c r="C759" s="6">
         <v>24024</v>
       </c>
@@ -14199,7 +14202,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="760" spans="3:7">
+    <row r="760" spans="1:8">
       <c r="C760" s="6">
         <v>24025</v>
       </c>
@@ -14213,6 +14216,448 @@
         <v>42</v>
       </c>
       <c r="G760" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="762" spans="1:8">
+      <c r="A762" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C762" s="6">
+        <v>24101</v>
+      </c>
+      <c r="D762" s="3">
+        <v>241</v>
+      </c>
+      <c r="E762" s="5">
+        <v>1</v>
+      </c>
+      <c r="F762" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G762" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H762" s="3">
+        <v>20465</v>
+      </c>
+    </row>
+    <row r="763" spans="1:8">
+      <c r="A763" s="1"/>
+      <c r="B763" s="1"/>
+      <c r="C763" s="6">
+        <v>24102</v>
+      </c>
+      <c r="D763" s="3">
+        <v>241</v>
+      </c>
+      <c r="E763" s="5">
+        <v>1</v>
+      </c>
+      <c r="F763" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G763" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H763" s="3">
+        <v>20466</v>
+      </c>
+    </row>
+    <row r="764" spans="1:8">
+      <c r="C764" s="6">
+        <v>24103</v>
+      </c>
+      <c r="D764" s="3">
+        <v>241</v>
+      </c>
+      <c r="E764" s="5">
+        <v>1</v>
+      </c>
+      <c r="F764" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G764" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H764" s="3">
+        <v>20467</v>
+      </c>
+    </row>
+    <row r="765" spans="1:8">
+      <c r="C765" s="6">
+        <v>24104</v>
+      </c>
+      <c r="D765" s="3">
+        <v>241</v>
+      </c>
+      <c r="E765" s="3">
+        <v>1</v>
+      </c>
+      <c r="F765" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G765" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H765" s="3">
+        <v>20468</v>
+      </c>
+    </row>
+    <row r="766" spans="1:8">
+      <c r="C766" s="6">
+        <v>24105</v>
+      </c>
+      <c r="D766" s="3">
+        <v>241</v>
+      </c>
+      <c r="E766" s="5">
+        <v>3</v>
+      </c>
+      <c r="F766" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G766" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="767" spans="1:8">
+      <c r="C767" s="6">
+        <v>24106</v>
+      </c>
+      <c r="D767" s="3">
+        <v>241</v>
+      </c>
+      <c r="E767" s="5">
+        <v>10</v>
+      </c>
+      <c r="F767" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G767" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="768" spans="1:8">
+      <c r="C768" s="6">
+        <v>24107</v>
+      </c>
+      <c r="D768" s="3">
+        <v>241</v>
+      </c>
+      <c r="E768" s="5">
+        <v>10</v>
+      </c>
+      <c r="F768" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G768" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="769" spans="3:7">
+      <c r="C769" s="6">
+        <v>24108</v>
+      </c>
+      <c r="D769" s="3">
+        <v>241</v>
+      </c>
+      <c r="E769" s="5">
+        <v>10</v>
+      </c>
+      <c r="F769" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G769" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="770" spans="3:7">
+      <c r="C770" s="6">
+        <v>24109</v>
+      </c>
+      <c r="D770" s="3">
+        <v>241</v>
+      </c>
+      <c r="E770" s="5">
+        <v>10</v>
+      </c>
+      <c r="F770" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G770" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="771" spans="3:7">
+      <c r="C771" s="6">
+        <v>24110</v>
+      </c>
+      <c r="D771" s="3">
+        <v>241</v>
+      </c>
+      <c r="E771" s="5">
+        <v>10</v>
+      </c>
+      <c r="F771" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G771" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="772" spans="3:7">
+      <c r="C772" s="6">
+        <v>24111</v>
+      </c>
+      <c r="D772" s="3">
+        <v>241</v>
+      </c>
+      <c r="E772" s="5">
+        <v>9</v>
+      </c>
+      <c r="F772" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G772" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="773" spans="3:7">
+      <c r="C773" s="6">
+        <v>24112</v>
+      </c>
+      <c r="D773" s="3">
+        <v>241</v>
+      </c>
+      <c r="E773" s="5">
+        <v>10</v>
+      </c>
+      <c r="F773" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G773" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="774" spans="3:7">
+      <c r="C774" s="6">
+        <v>24113</v>
+      </c>
+      <c r="D774" s="3">
+        <v>241</v>
+      </c>
+      <c r="E774" s="5">
+        <v>9</v>
+      </c>
+      <c r="F774" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G774" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="775" spans="3:7">
+      <c r="C775" s="6">
+        <v>24114</v>
+      </c>
+      <c r="D775" s="3">
+        <v>241</v>
+      </c>
+      <c r="E775" s="5">
+        <v>9</v>
+      </c>
+      <c r="F775" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G775" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="776" spans="3:7">
+      <c r="C776" s="6">
+        <v>24115</v>
+      </c>
+      <c r="D776" s="3">
+        <v>241</v>
+      </c>
+      <c r="E776" s="5">
+        <v>9</v>
+      </c>
+      <c r="F776" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G776" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="777" spans="3:7">
+      <c r="C777" s="6">
+        <v>24116</v>
+      </c>
+      <c r="D777" s="3">
+        <v>241</v>
+      </c>
+      <c r="E777" s="5">
+        <v>2</v>
+      </c>
+      <c r="F777" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G777" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="778" spans="3:7">
+      <c r="C778" s="6">
+        <v>24117</v>
+      </c>
+      <c r="D778" s="3">
+        <v>241</v>
+      </c>
+      <c r="E778" s="3">
+        <v>9</v>
+      </c>
+      <c r="F778" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G778" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="779" spans="3:7">
+      <c r="C779" s="6">
+        <v>24118</v>
+      </c>
+      <c r="D779" s="3">
+        <v>241</v>
+      </c>
+      <c r="E779" s="5">
+        <v>9</v>
+      </c>
+      <c r="F779" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G779" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="780" spans="3:7">
+      <c r="C780" s="6">
+        <v>24119</v>
+      </c>
+      <c r="D780" s="3">
+        <v>241</v>
+      </c>
+      <c r="E780" s="5">
+        <v>10</v>
+      </c>
+      <c r="F780" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G780" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="781" spans="3:7">
+      <c r="C781" s="6">
+        <v>24120</v>
+      </c>
+      <c r="D781" s="3">
+        <v>241</v>
+      </c>
+      <c r="E781" s="5">
+        <v>9</v>
+      </c>
+      <c r="F781" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G781" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="782" spans="3:7">
+      <c r="C782" s="6">
+        <v>24121</v>
+      </c>
+      <c r="D782" s="3">
+        <v>241</v>
+      </c>
+      <c r="E782" s="5">
+        <v>5</v>
+      </c>
+      <c r="F782" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G782" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="783" spans="3:7">
+      <c r="C783" s="6">
+        <v>24122</v>
+      </c>
+      <c r="D783" s="3">
+        <v>241</v>
+      </c>
+      <c r="E783" s="5">
+        <v>6</v>
+      </c>
+      <c r="F783" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G783" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="784" spans="3:7">
+      <c r="C784" s="6">
+        <v>24123</v>
+      </c>
+      <c r="D784" s="3">
+        <v>241</v>
+      </c>
+      <c r="E784" s="5">
+        <v>7</v>
+      </c>
+      <c r="F784" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G784" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="785" spans="3:7">
+      <c r="C785" s="6">
+        <v>24124</v>
+      </c>
+      <c r="D785" s="3">
+        <v>241</v>
+      </c>
+      <c r="E785" s="5">
+        <v>8</v>
+      </c>
+      <c r="F785" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G785" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="786" spans="3:7">
+      <c r="C786" s="6">
+        <v>24125</v>
+      </c>
+      <c r="D786" s="3">
+        <v>241</v>
+      </c>
+      <c r="E786" s="5">
+        <v>9</v>
+      </c>
+      <c r="F786" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G786" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -14333,10 +14778,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -14351,10 +14796,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -14369,10 +14814,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -14387,10 +14832,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -14407,10 +14852,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -14505,10 +14950,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -252,7 +252,7 @@
     <t>#先锋240青野拾光</t>
   </si>
   <si>
-    <t>#先锋241</t>
+    <t>#先锋241逐光之路</t>
   </si>
   <si>
     <t>Center</t>

--- a/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="81">
   <si>
     <t>Id</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>#先锋241逐光之路</t>
+  </si>
+  <si>
+    <t>#先锋242</t>
   </si>
   <si>
     <t>Center</t>
@@ -1280,7 +1283,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O786"/>
+  <dimension ref="A3:O812"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -14627,7 +14630,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="785" spans="3:7">
+    <row r="785" spans="1:8">
       <c r="C785" s="6">
         <v>24124</v>
       </c>
@@ -14644,7 +14647,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="786" spans="3:7">
+    <row r="786" spans="1:8">
       <c r="C786" s="6">
         <v>24125</v>
       </c>
@@ -14658,6 +14661,448 @@
         <v>42</v>
       </c>
       <c r="G786" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="788" spans="1:8">
+      <c r="A788" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C788" s="6">
+        <v>24201</v>
+      </c>
+      <c r="D788" s="3">
+        <v>242</v>
+      </c>
+      <c r="E788" s="5">
+        <v>1</v>
+      </c>
+      <c r="F788" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G788" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H788" s="3">
+        <v>20485</v>
+      </c>
+    </row>
+    <row r="789" spans="1:8">
+      <c r="A789" s="1"/>
+      <c r="B789" s="1"/>
+      <c r="C789" s="6">
+        <v>24202</v>
+      </c>
+      <c r="D789" s="3">
+        <v>242</v>
+      </c>
+      <c r="E789" s="5">
+        <v>1</v>
+      </c>
+      <c r="F789" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G789" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H789" s="3">
+        <v>20486</v>
+      </c>
+    </row>
+    <row r="790" spans="1:8">
+      <c r="C790" s="6">
+        <v>24203</v>
+      </c>
+      <c r="D790" s="3">
+        <v>242</v>
+      </c>
+      <c r="E790" s="5">
+        <v>1</v>
+      </c>
+      <c r="F790" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G790" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H790" s="3">
+        <v>20487</v>
+      </c>
+    </row>
+    <row r="791" spans="1:8">
+      <c r="C791" s="6">
+        <v>24204</v>
+      </c>
+      <c r="D791" s="3">
+        <v>242</v>
+      </c>
+      <c r="E791" s="3">
+        <v>1</v>
+      </c>
+      <c r="F791" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G791" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H791" s="3">
+        <v>20488</v>
+      </c>
+    </row>
+    <row r="792" spans="1:8">
+      <c r="C792" s="6">
+        <v>24205</v>
+      </c>
+      <c r="D792" s="3">
+        <v>242</v>
+      </c>
+      <c r="E792" s="5">
+        <v>3</v>
+      </c>
+      <c r="F792" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G792" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="793" spans="1:8">
+      <c r="C793" s="6">
+        <v>24206</v>
+      </c>
+      <c r="D793" s="3">
+        <v>242</v>
+      </c>
+      <c r="E793" s="5">
+        <v>10</v>
+      </c>
+      <c r="F793" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G793" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="794" spans="1:8">
+      <c r="C794" s="6">
+        <v>24207</v>
+      </c>
+      <c r="D794" s="3">
+        <v>242</v>
+      </c>
+      <c r="E794" s="5">
+        <v>10</v>
+      </c>
+      <c r="F794" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G794" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="795" spans="1:8">
+      <c r="C795" s="6">
+        <v>24208</v>
+      </c>
+      <c r="D795" s="3">
+        <v>242</v>
+      </c>
+      <c r="E795" s="5">
+        <v>10</v>
+      </c>
+      <c r="F795" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G795" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="796" spans="1:8">
+      <c r="C796" s="6">
+        <v>24209</v>
+      </c>
+      <c r="D796" s="3">
+        <v>242</v>
+      </c>
+      <c r="E796" s="5">
+        <v>10</v>
+      </c>
+      <c r="F796" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G796" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="797" spans="1:8">
+      <c r="C797" s="6">
+        <v>24210</v>
+      </c>
+      <c r="D797" s="3">
+        <v>242</v>
+      </c>
+      <c r="E797" s="5">
+        <v>10</v>
+      </c>
+      <c r="F797" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G797" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="798" spans="1:8">
+      <c r="C798" s="6">
+        <v>24211</v>
+      </c>
+      <c r="D798" s="3">
+        <v>242</v>
+      </c>
+      <c r="E798" s="5">
+        <v>9</v>
+      </c>
+      <c r="F798" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G798" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="799" spans="1:8">
+      <c r="C799" s="6">
+        <v>24212</v>
+      </c>
+      <c r="D799" s="3">
+        <v>242</v>
+      </c>
+      <c r="E799" s="5">
+        <v>10</v>
+      </c>
+      <c r="F799" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G799" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="800" spans="1:8">
+      <c r="C800" s="6">
+        <v>24213</v>
+      </c>
+      <c r="D800" s="3">
+        <v>242</v>
+      </c>
+      <c r="E800" s="5">
+        <v>9</v>
+      </c>
+      <c r="F800" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G800" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="801" spans="3:7">
+      <c r="C801" s="6">
+        <v>24214</v>
+      </c>
+      <c r="D801" s="3">
+        <v>242</v>
+      </c>
+      <c r="E801" s="5">
+        <v>9</v>
+      </c>
+      <c r="F801" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G801" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="802" spans="3:7">
+      <c r="C802" s="6">
+        <v>24215</v>
+      </c>
+      <c r="D802" s="3">
+        <v>242</v>
+      </c>
+      <c r="E802" s="5">
+        <v>9</v>
+      </c>
+      <c r="F802" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G802" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="803" spans="3:7">
+      <c r="C803" s="6">
+        <v>24216</v>
+      </c>
+      <c r="D803" s="3">
+        <v>242</v>
+      </c>
+      <c r="E803" s="5">
+        <v>2</v>
+      </c>
+      <c r="F803" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G803" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="804" spans="3:7">
+      <c r="C804" s="6">
+        <v>24217</v>
+      </c>
+      <c r="D804" s="3">
+        <v>242</v>
+      </c>
+      <c r="E804" s="3">
+        <v>9</v>
+      </c>
+      <c r="F804" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G804" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="805" spans="3:7">
+      <c r="C805" s="6">
+        <v>24218</v>
+      </c>
+      <c r="D805" s="3">
+        <v>242</v>
+      </c>
+      <c r="E805" s="5">
+        <v>9</v>
+      </c>
+      <c r="F805" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G805" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="806" spans="3:7">
+      <c r="C806" s="6">
+        <v>24219</v>
+      </c>
+      <c r="D806" s="3">
+        <v>242</v>
+      </c>
+      <c r="E806" s="5">
+        <v>10</v>
+      </c>
+      <c r="F806" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G806" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="807" spans="3:7">
+      <c r="C807" s="6">
+        <v>24220</v>
+      </c>
+      <c r="D807" s="3">
+        <v>242</v>
+      </c>
+      <c r="E807" s="5">
+        <v>9</v>
+      </c>
+      <c r="F807" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G807" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="808" spans="3:7">
+      <c r="C808" s="6">
+        <v>24221</v>
+      </c>
+      <c r="D808" s="3">
+        <v>242</v>
+      </c>
+      <c r="E808" s="5">
+        <v>5</v>
+      </c>
+      <c r="F808" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G808" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="809" spans="3:7">
+      <c r="C809" s="6">
+        <v>24222</v>
+      </c>
+      <c r="D809" s="3">
+        <v>242</v>
+      </c>
+      <c r="E809" s="5">
+        <v>6</v>
+      </c>
+      <c r="F809" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G809" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="810" spans="3:7">
+      <c r="C810" s="6">
+        <v>24223</v>
+      </c>
+      <c r="D810" s="3">
+        <v>242</v>
+      </c>
+      <c r="E810" s="5">
+        <v>7</v>
+      </c>
+      <c r="F810" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G810" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="811" spans="3:7">
+      <c r="C811" s="6">
+        <v>24224</v>
+      </c>
+      <c r="D811" s="3">
+        <v>242</v>
+      </c>
+      <c r="E811" s="5">
+        <v>8</v>
+      </c>
+      <c r="F811" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G811" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="812" spans="3:7">
+      <c r="C812" s="6">
+        <v>24225</v>
+      </c>
+      <c r="D812" s="3">
+        <v>242</v>
+      </c>
+      <c r="E812" s="5">
+        <v>9</v>
+      </c>
+      <c r="F812" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G812" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -14778,10 +15223,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -14796,10 +15241,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -14814,10 +15259,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -14832,10 +15277,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -14852,10 +15297,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -14950,10 +15395,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/LocalhostOld/StartSceneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\LocalhostOld\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -255,7 +255,7 @@
     <t>#先锋241逐光之路</t>
   </si>
   <si>
-    <t>#先锋242</t>
+    <t>#先锋242苍风之誓</t>
   </si>
   <si>
     <t>Center</t>
